--- a/data/dividends_info_20260703.xlsx
+++ b/data/dividends_info_20260703.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>62.29000091552734</v>
+        <v>62.77999877929688</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1444854690595537</v>
+        <v>0.1433577600349994</v>
       </c>
       <c r="J2" t="n">
         <v>255</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65.90000152587891</v>
+        <v>66.25</v>
       </c>
       <c r="I3" t="n">
-        <v>1.06221545340194</v>
+        <v>1.056603773584906</v>
       </c>
       <c r="J3" t="n">
         <v>234</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.359999656677246</v>
+        <v>9.739999771118164</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6410256645383222</v>
+        <v>0.6160164415805928</v>
       </c>
       <c r="J4" t="n">
         <v>164</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>62.27999877929688</v>
+        <v>62.77999877929688</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1445086733526363</v>
+        <v>0.1433577600349994</v>
       </c>
       <c r="J6" t="n">
         <v>164</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.099999904632568</v>
+        <v>2.109999895095825</v>
       </c>
       <c r="I7" t="n">
-        <v>3.666666833181238</v>
+        <v>3.649289280960038</v>
       </c>
       <c r="J7" t="n">
         <v>143</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>20.36499977111816</v>
+        <v>20.44499969482422</v>
       </c>
       <c r="I8" t="n">
-        <v>1.325804090520623</v>
+        <v>1.320616307313285</v>
       </c>
       <c r="J8" t="n">
         <v>143</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>5.989999771118164</v>
       </c>
       <c r="I9" t="n">
-        <v>3.333333333333333</v>
+        <v>3.338898291187508</v>
       </c>
       <c r="J9" t="n">
         <v>136</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.699999809265137</v>
+        <v>7.900000095367432</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7792207985226717</v>
+        <v>0.7594936617175999</v>
       </c>
       <c r="J10" t="n">
         <v>108</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.960000038146973</v>
+        <v>4.980000019073486</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7661290263658259</v>
+        <v>0.7630522059128382</v>
       </c>
       <c r="J13" t="n">
         <v>87</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>20.36499977111816</v>
+        <v>20.44499969482422</v>
       </c>
       <c r="I14" t="n">
-        <v>1.325804090520623</v>
+        <v>1.320616307313285</v>
       </c>
       <c r="J14" t="n">
         <v>80</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>62.27999877929688</v>
+        <v>62.77999877929688</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1445086733526363</v>
+        <v>0.1433577600349994</v>
       </c>
       <c r="J15" t="n">
         <v>80</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.960000038146973</v>
+        <v>6</v>
       </c>
       <c r="I16" t="n">
-        <v>5.03355701476259</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
         <v>73</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.960000038146973</v>
+        <v>4.980000019073486</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7661290263658259</v>
+        <v>0.7630522059128382</v>
       </c>
       <c r="J18" t="n">
         <v>31</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.760000228881836</v>
+        <v>5.840000152587891</v>
       </c>
       <c r="I19" t="n">
-        <v>4.340277605310641</v>
+        <v>4.280821805958635</v>
       </c>
       <c r="J19" t="n">
         <v>24</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>10.19799995422363</v>
+        <v>10.26000022888184</v>
       </c>
       <c r="I21" t="n">
-        <v>2.549519525074303</v>
+        <v>2.534113003897423</v>
       </c>
       <c r="J21" t="n">
         <v>17</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.97999954223633</v>
+        <v>14.69999980926514</v>
       </c>
       <c r="I22" t="n">
-        <v>4.005340576335073</v>
+        <v>4.081632706021065</v>
       </c>
       <c r="J22" t="n">
         <v>17</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.907999992370605</v>
+        <v>2.881999969482422</v>
       </c>
       <c r="I23" t="n">
-        <v>7.565337021223844</v>
+        <v>7.633587867091816</v>
       </c>
       <c r="J23" t="n">
         <v>17</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.914999961853027</v>
+        <v>6.980000019073486</v>
       </c>
       <c r="I25" t="n">
-        <v>3.47071585428739</v>
+        <v>3.43839540607705</v>
       </c>
       <c r="J25" t="n">
         <v>17</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>19.75</v>
+        <v>19.89999961853027</v>
       </c>
       <c r="I26" t="n">
-        <v>1.90379746835443</v>
+        <v>1.889447272400348</v>
       </c>
       <c r="J26" t="n">
         <v>17</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.820000171661377</v>
+        <v>5.829999923706055</v>
       </c>
       <c r="I27" t="n">
-        <v>2.061855609288493</v>
+        <v>2.058319066387184</v>
       </c>
       <c r="J27" t="n">
         <v>10</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>3.079999923706055</v>
+        <v>3.119999885559082</v>
       </c>
       <c r="I29" t="n">
-        <v>4.870129990766698</v>
+        <v>4.807692484037417</v>
       </c>
       <c r="J29" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.240000009536743</v>
+        <v>2.339999914169312</v>
       </c>
       <c r="I30" t="n">
-        <v>3.794642840987262</v>
+        <v>3.63247876571716</v>
       </c>
       <c r="J30" t="n">
         <v>3</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.690000057220459</v>
+        <v>4.760000228881836</v>
       </c>
       <c r="I31" t="n">
-        <v>1.492537295223098</v>
+        <v>1.47058816458174</v>
       </c>
       <c r="J31" t="n">
         <v>3</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>38.25</v>
+        <v>38.45000076293945</v>
       </c>
       <c r="I32" t="n">
-        <v>0.392156862745098</v>
+        <v>0.3901170273696834</v>
       </c>
       <c r="J32" t="n">
         <v>3</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5.349999904632568</v>
+        <v>5.099999904632568</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7476635647294868</v>
+        <v>0.784313740156468</v>
       </c>
       <c r="J33" t="n">
         <v>-4</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>21.73999977111816</v>
+        <v>22.05999946594238</v>
       </c>
       <c r="I34" t="n">
-        <v>1.149954013946807</v>
+        <v>1.133272919548188</v>
       </c>
       <c r="J34" t="n">
         <v>-11</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>31</v>
+        <v>30.89999961853027</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6290322580645161</v>
+        <v>0.6310679689557711</v>
       </c>
       <c r="J35" t="n">
         <v>-11</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.909999966621399</v>
+        <v>1.879999995231628</v>
       </c>
       <c r="I36" t="n">
-        <v>1.727748721293108</v>
+        <v>1.755319153388305</v>
       </c>
       <c r="J36" t="n">
         <v>-11</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.255000114440918</v>
+        <v>5.309999942779541</v>
       </c>
       <c r="I37" t="n">
-        <v>5.518553638144938</v>
+        <v>5.461393655838691</v>
       </c>
       <c r="J37" t="n">
         <v>-11</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.752000093460083</v>
+        <v>3.799999952316284</v>
       </c>
       <c r="I38" t="n">
-        <v>4.264392217870349</v>
+        <v>4.210526368624617</v>
       </c>
       <c r="J38" t="n">
         <v>-11</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.53600001335144</v>
+        <v>2.569999933242798</v>
       </c>
       <c r="I39" t="n">
-        <v>5.465299655769076</v>
+        <v>5.392996249035542</v>
       </c>
       <c r="J39" t="n">
         <v>-11</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>51.52999877929688</v>
+        <v>52.52999877929688</v>
       </c>
       <c r="I40" t="n">
-        <v>1.222588812195187</v>
+        <v>1.199314705197168</v>
       </c>
       <c r="J40" t="n">
         <v>-11</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6.175000190734863</v>
+        <v>6.224999904632568</v>
       </c>
       <c r="I41" t="n">
-        <v>2.267206407702785</v>
+        <v>2.248996018390518</v>
       </c>
       <c r="J41" t="n">
         <v>-11</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>16.75</v>
+        <v>16.25</v>
       </c>
       <c r="I42" t="n">
-        <v>4.656716417910448</v>
+        <v>4.8</v>
       </c>
       <c r="J42" t="n">
         <v>-11</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>29.20999908447266</v>
+        <v>29.1299991607666</v>
       </c>
       <c r="I43" t="n">
-        <v>2.909962432870598</v>
+        <v>2.917954083379489</v>
       </c>
       <c r="J43" t="n">
         <v>-11</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>62.27999877929688</v>
+        <v>62.77999877929688</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1445086733526363</v>
+        <v>0.1433577600349994</v>
       </c>
       <c r="J44" t="n">
         <v>-11</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.360000014305115</v>
+        <v>1.340000033378601</v>
       </c>
       <c r="I45" t="n">
-        <v>0.7352941099128922</v>
+        <v>0.746268638127311</v>
       </c>
       <c r="J45" t="n">
         <v>-11</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.271999835968018</v>
+        <v>6.300000190734863</v>
       </c>
       <c r="I46" t="n">
-        <v>2.890625075598686</v>
+        <v>2.877777690651978</v>
       </c>
       <c r="J46" t="n">
         <v>-11</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>9.560000419616699</v>
+        <v>10.11999988555908</v>
       </c>
       <c r="I47" t="n">
-        <v>2.719665152592373</v>
+        <v>2.569169989527488</v>
       </c>
       <c r="J47" t="n">
         <v>-11</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>10.22500038146973</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="I48" t="n">
-        <v>2.709046353699837</v>
+        <v>2.689320338548821</v>
       </c>
       <c r="J48" t="n">
         <v>-11</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.059999942779541</v>
+        <v>1.120000004768372</v>
       </c>
       <c r="I49" t="n">
-        <v>1.273584974410487</v>
+        <v>1.205357137725365</v>
       </c>
       <c r="J49" t="n">
         <v>-18</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.013999938964844</v>
+        <v>3.00600004196167</v>
       </c>
       <c r="I50" t="n">
-        <v>3.649635110403467</v>
+        <v>3.659347919643264</v>
       </c>
       <c r="J50" t="n">
         <v>-18</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.720000028610229</v>
+        <v>1.700000047683716</v>
       </c>
       <c r="I51" t="n">
-        <v>1.395348813999273</v>
+        <v>1.41176466628342</v>
       </c>
       <c r="J51" t="n">
         <v>-18</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.980000019073486</v>
+        <v>3.009999990463257</v>
       </c>
       <c r="I52" t="n">
-        <v>5.36912748241343</v>
+        <v>5.315614634781944</v>
       </c>
       <c r="J52" t="n">
         <v>-25</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.8650000095367432</v>
+        <v>0.8600000143051147</v>
       </c>
       <c r="I53" t="n">
-        <v>2.890173378540068</v>
+        <v>2.90697669583182</v>
       </c>
       <c r="J53" t="n">
         <v>-25</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>27.60000038146973</v>
+        <v>27.45000076293945</v>
       </c>
       <c r="I54" t="n">
-        <v>4.021739074848851</v>
+        <v>4.043715734604362</v>
       </c>
       <c r="J54" t="n">
         <v>-29</v>
@@ -4356,7 +4356,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4475,7 +4475,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4509,7 +4509,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4519,14 +4519,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4536,14 +4536,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4560,7 +4560,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4570,14 +4570,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4587,14 +4587,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4604,14 +4604,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4621,14 +4621,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>CASTELLO SGR S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4645,7 +4645,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4655,14 +4655,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4672,14 +4672,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4696,7 +4696,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4706,14 +4706,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CASTELLO SGR S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4764,7 +4764,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4781,7 +4781,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4791,14 +4791,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4808,14 +4808,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4825,14 +4825,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4842,14 +4842,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4859,14 +4859,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4876,14 +4876,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4900,7 +4900,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4910,14 +4910,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4927,14 +4927,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4944,14 +4944,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4968,7 +4968,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4978,14 +4978,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4995,14 +4995,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5012,14 +5012,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5036,7 +5036,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5046,14 +5046,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5070,7 +5070,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5080,14 +5080,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5097,14 +5097,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5114,14 +5114,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5138,7 +5138,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5155,7 +5155,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5172,7 +5172,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5182,14 +5182,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5206,7 +5206,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5216,14 +5216,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5233,14 +5233,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5257,7 +5257,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5274,7 +5274,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5284,14 +5284,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5325,7 +5325,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5342,7 +5342,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5393,7 +5393,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5403,14 +5403,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5420,14 +5420,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5437,14 +5437,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5454,14 +5454,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5471,14 +5471,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5512,7 +5512,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5522,14 +5522,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5539,14 +5539,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5556,14 +5556,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5580,7 +5580,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5590,14 +5590,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5607,14 +5607,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5631,7 +5631,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5641,14 +5641,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5658,14 +5658,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5682,7 +5682,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5692,14 +5692,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5709,14 +5709,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5726,14 +5726,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5750,7 +5750,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5760,14 +5760,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5777,14 +5777,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5794,14 +5794,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5811,14 +5811,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5852,7 +5852,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5862,14 +5862,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5879,14 +5879,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
